--- a/patient_settings_uitgebreid.xlsx
+++ b/patient_settings_uitgebreid.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Vivian\Desktop\Master onderzoek\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D74B6C91-FE3E-4F11-B1CF-D655E95AC7F7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5EE97CCD-B687-4908-8A5E-E2759C4D7E45}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -19,7 +19,7 @@
     <sheet name="Microbiologie" sheetId="4" r:id="rId4"/>
     <sheet name="Laboratorium" sheetId="5" r:id="rId5"/>
   </sheets>
-  <calcPr calcId="191029" refMode="R1C1"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="94" uniqueCount="81">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="107" uniqueCount="90">
   <si>
     <t>PATIËNTINSTELLINGEN</t>
   </si>
@@ -60,6 +60,9 @@
     <t>geslacht</t>
   </si>
   <si>
+    <t>man</t>
+  </si>
+  <si>
     <t>Kies man, vrouw, anders of onbekend.</t>
   </si>
   <si>
@@ -150,30 +153,33 @@
     <t>CONTROLE DEELCONTACTEN</t>
   </si>
   <si>
-    <t>essentiële hypertensie</t>
-  </si>
-  <si>
-    <t>Volgorde 1 treedt het eerst op. Vul aantallen voor alle episodes in, of laat de hele kolom leeg.</t>
+    <t>Essentiële hypertensie</t>
+  </si>
+  <si>
+    <t>Langdurig bekend, meestal redelijk gereguleerd met enkele hogere metingen</t>
   </si>
   <si>
     <t>Totaal per episode</t>
   </si>
   <si>
-    <t>diabetes mellitus type 2</t>
-  </si>
-  <si>
-    <t>Gebruik unieke volgnummers. De som van kolom D moet gelijk zijn aan het totaal op Patient.</t>
+    <t>Diabetes mellitus type 2</t>
+  </si>
+  <si>
+    <t>Jaarcontroles, wisselende HbA1c-waarden en aandacht voor leefstijl en medicatie</t>
   </si>
   <si>
     <t>Totaal tabblad Patient</t>
   </si>
   <si>
-    <t>De patiëntspecifieke omschrijving is bindend. Laat kolom D volledig leeg voor automatische verdeling.</t>
-  </si>
-  <si>
     <t>Controle</t>
   </si>
   <si>
+    <t>Valincident met huidwond</t>
+  </si>
+  <si>
+    <t>Cerebraal infarct</t>
+  </si>
+  <si>
     <t>allergeen</t>
   </si>
   <si>
@@ -189,6 +195,9 @@
     <t>status</t>
   </si>
   <si>
+    <t>Kiwi</t>
+  </si>
+  <si>
     <t>Alleen gebruikt als allergie_modus op Zelf invoeren staat.</t>
   </si>
   <si>
@@ -264,29 +273,47 @@
     <t>Bij Geen blijft de lijst met laboratoriumuitslagen leeg.</t>
   </si>
   <si>
-    <t>P007</t>
-  </si>
-  <si>
-    <t>vrouw</t>
-  </si>
-  <si>
-    <t>Triggerfinger</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Reumatroide artritis </t>
-  </si>
-  <si>
-    <t>Tendovaginitis</t>
-  </si>
-  <si>
-    <t>Kiwi</t>
+    <t>rookstatus</t>
+  </si>
+  <si>
+    <t>Laat op Automatisch staan of vul zelf in, bijvoorbeeld: voormalig roker, 20 pack-years, gestopt in 2012.</t>
+  </si>
+  <si>
+    <t>alcoholgebruik</t>
+  </si>
+  <si>
+    <t>Laat op Automatisch staan of vul zelf een realistisch gebruik in, bijvoorbeeld: 4 eenheden per week.</t>
+  </si>
+  <si>
+    <t>familieanamnese</t>
+  </si>
+  <si>
+    <t>Laat op Automatisch staan of specificeer klinisch relevante familieanamnese; bijvoorbeeld hart- en vaatziekten bij een eerstegraads familielid.</t>
+  </si>
+  <si>
+    <t>woonsituatie</t>
+  </si>
+  <si>
+    <t>Laat op Automatisch staan of specificeer bijvoorbeeld alleenwonend, samenwonend, mantelzorg of thuiszorg.</t>
+  </si>
+  <si>
+    <t>beroep_functionele_context</t>
+  </si>
+  <si>
+    <t>Laat op Automatisch staan of beschrijf beroep/dagbesteding en relevante zelfstandigheid, mobiliteit of hulpmiddelen.</t>
+  </si>
+  <si>
+    <t>P010</t>
+  </si>
+  <si>
+    <t>1 pakje per dag</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="10">
+  <fonts count="11">
     <font>
       <sz val="11"/>
       <name val="Carlito"/>
@@ -338,8 +365,13 @@
       <sz val="11"/>
       <name val="Carlito"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF1F1F1F"/>
+      <name val="Carlito"/>
+    </font>
   </fonts>
-  <fills count="12">
+  <fills count="15">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -396,6 +428,21 @@
         <fgColor rgb="FFE2F0D9"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDDEBF7"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFF2CC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="47">
     <border>
@@ -976,7 +1023,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="53">
+  <cellXfs count="57">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1124,6 +1171,18 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="4" borderId="46" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="12" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="13" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="14" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
@@ -1144,7 +1203,7 @@
         <color rgb="FF7F6000"/>
       </font>
       <fill>
-        <patternFill patternType="solid">
+        <patternFill>
           <bgColor rgb="FFFFF2CC"/>
         </patternFill>
       </fill>
@@ -1155,7 +1214,7 @@
         <color rgb="FF9C0006"/>
       </font>
       <fill>
-        <patternFill patternType="solid">
+        <patternFill>
           <bgColor rgb="FFF4CCCC"/>
         </patternFill>
       </fill>
@@ -1166,7 +1225,7 @@
         <color rgb="FF375623"/>
       </font>
       <fill>
-        <patternFill patternType="solid">
+        <patternFill>
           <bgColor rgb="FFC6E0B4"/>
         </patternFill>
       </fill>
@@ -1177,7 +1236,7 @@
         <color rgb="FF9C0006"/>
       </font>
       <fill>
-        <patternFill patternType="solid">
+        <patternFill>
           <bgColor rgb="FFF4CCCC"/>
         </patternFill>
       </fill>
@@ -1390,7 +1449,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C16"/>
+  <dimension ref="A1:C21"/>
   <sheetFormatPr defaultRowHeight="13.8"/>
   <cols>
     <col min="1" max="1" width="25" customWidth="1"/>
@@ -1399,11 +1458,11 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" ht="30" customHeight="1">
-      <c r="A1" s="51" t="s">
+      <c r="A1" s="55" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="51"/>
-      <c r="C1" s="51"/>
+      <c r="B1" s="55"/>
+      <c r="C1" s="55"/>
     </row>
     <row r="3" spans="1:3">
       <c r="A3" s="1" t="s">
@@ -1421,7 +1480,7 @@
         <v>4</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>75</v>
+        <v>88</v>
       </c>
       <c r="C4" s="6" t="s">
         <v>5</v>
@@ -1432,131 +1491,186 @@
         <v>6</v>
       </c>
       <c r="B5" s="8" t="s">
-        <v>76</v>
+        <v>7</v>
       </c>
       <c r="C5" s="9" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="6" spans="1:3" ht="36" customHeight="1">
       <c r="A6" s="7" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B6" s="8">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="C6" s="9" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="7" spans="1:3" ht="36" customHeight="1">
       <c r="A7" s="7" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B7" s="8">
         <v>5</v>
       </c>
       <c r="C7" s="9" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="8" spans="1:3" ht="36" customHeight="1">
       <c r="A8" s="7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B8" s="8">
         <v>10</v>
       </c>
       <c r="C8" s="9" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="9" spans="1:3" ht="36" customHeight="1">
       <c r="A9" s="7" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B9" s="8" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C9" s="9" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="10" spans="1:3" ht="36" customHeight="1">
       <c r="A10" s="7" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B10" s="8" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C10" s="9" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="11" spans="1:3" ht="36" customHeight="1">
       <c r="A11" s="7" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B11" s="8" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C11" s="9" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="12" spans="1:3" ht="36" customHeight="1">
       <c r="A12" s="7" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B12" s="8" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C12" s="9" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="13" spans="1:3" ht="36" customHeight="1">
       <c r="A13" s="7" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B13" s="8" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C13" s="9" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="14" spans="1:3" ht="36" customHeight="1">
       <c r="A14" s="7" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B14" s="8" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C14" s="9" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
     <row r="15" spans="1:3" ht="36" customHeight="1">
       <c r="A15" s="7" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B15" s="8" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C15" s="9" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
     <row r="16" spans="1:3" ht="36" customHeight="1">
       <c r="A16" s="10" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B16" s="11" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C16" s="12" t="s">
-        <v>32</v>
+        <v>33</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" ht="48" customHeight="1">
+      <c r="A17" s="52" t="s">
+        <v>78</v>
+      </c>
+      <c r="B17" s="53" t="s">
+        <v>89</v>
+      </c>
+      <c r="C17" s="54" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" ht="48" customHeight="1">
+      <c r="A18" s="52" t="s">
+        <v>80</v>
+      </c>
+      <c r="B18" s="53" t="s">
+        <v>28</v>
+      </c>
+      <c r="C18" s="54" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" ht="48" customHeight="1">
+      <c r="A19" s="52" t="s">
+        <v>82</v>
+      </c>
+      <c r="B19" s="53" t="s">
+        <v>28</v>
+      </c>
+      <c r="C19" s="54" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" ht="48" customHeight="1">
+      <c r="A20" s="52" t="s">
+        <v>84</v>
+      </c>
+      <c r="B20" s="53" t="s">
+        <v>28</v>
+      </c>
+      <c r="C20" s="54" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" ht="48" customHeight="1">
+      <c r="A21" s="52" t="s">
+        <v>86</v>
+      </c>
+      <c r="B21" s="53" t="s">
+        <v>28</v>
+      </c>
+      <c r="C21" s="54" t="s">
+        <v>87</v>
       </c>
     </row>
   </sheetData>
@@ -1606,39 +1720,37 @@
   <sheetData>
     <row r="1" spans="1:8">
       <c r="A1" s="13" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B1" s="14" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C1" s="14" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D1" s="14" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E1" s="15" t="s">
         <v>3</v>
       </c>
-      <c r="G1" s="52" t="s">
-        <v>36</v>
-      </c>
-      <c r="H1" s="52"/>
+      <c r="G1" s="56" t="s">
+        <v>37</v>
+      </c>
+      <c r="H1" s="56"/>
     </row>
     <row r="2" spans="1:8" ht="42" customHeight="1">
-      <c r="A2" s="16">
+      <c r="A2" s="51">
         <v>1</v>
       </c>
-      <c r="B2" s="17" t="s">
-        <v>37</v>
-      </c>
-      <c r="C2" s="17"/>
-      <c r="D2" s="17"/>
-      <c r="E2" s="18" t="s">
+      <c r="B2" s="51" t="s">
         <v>38</v>
       </c>
+      <c r="C2" s="51" t="s">
+        <v>39</v>
+      </c>
       <c r="G2" s="22" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="H2" s="23">
         <f>SUM(D2:D30)</f>
@@ -1646,19 +1758,17 @@
       </c>
     </row>
     <row r="3" spans="1:8" ht="42" customHeight="1">
-      <c r="A3" s="16">
+      <c r="A3" s="51">
         <v>2</v>
       </c>
-      <c r="B3" s="17" t="s">
-        <v>40</v>
-      </c>
-      <c r="C3" s="17"/>
-      <c r="D3" s="17"/>
-      <c r="E3" s="18" t="s">
+      <c r="B3" s="51" t="s">
         <v>41</v>
       </c>
+      <c r="C3" s="51" t="s">
+        <v>42</v>
+      </c>
       <c r="G3" s="22" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="H3" s="23">
         <f>Patient!B8</f>
@@ -1666,16 +1776,11 @@
       </c>
     </row>
     <row r="4" spans="1:8" ht="42" customHeight="1">
-      <c r="A4" s="16">
-        <v>3</v>
-      </c>
-      <c r="B4" s="17" t="s">
-        <v>77</v>
-      </c>
-      <c r="C4" s="17"/>
-      <c r="D4" s="17"/>
-      <c r="E4" s="18" t="s">
-        <v>43</v>
+      <c r="A4" s="51">
+        <v>11</v>
+      </c>
+      <c r="B4" s="51" t="s">
+        <v>45</v>
       </c>
       <c r="G4" s="22" t="s">
         <v>44</v>
@@ -1687,67 +1792,47 @@
     </row>
     <row r="5" spans="1:8" ht="42" customHeight="1">
       <c r="A5" s="16">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="B5" s="17" t="s">
-        <v>78</v>
+        <v>46</v>
       </c>
       <c r="C5" s="17"/>
-      <c r="D5" s="17"/>
-      <c r="E5" s="18"/>
     </row>
     <row r="6" spans="1:8" ht="42" customHeight="1">
-      <c r="A6" s="16">
-        <v>5</v>
-      </c>
-      <c r="B6" s="17" t="s">
-        <v>79</v>
-      </c>
+      <c r="A6" s="16"/>
+      <c r="B6" s="17"/>
       <c r="C6" s="17"/>
-      <c r="D6" s="17"/>
-      <c r="E6" s="18"/>
     </row>
     <row r="7" spans="1:8" ht="42" customHeight="1">
       <c r="A7" s="16"/>
       <c r="B7" s="17"/>
       <c r="C7" s="17"/>
-      <c r="D7" s="17"/>
-      <c r="E7" s="18"/>
     </row>
     <row r="8" spans="1:8" ht="42" customHeight="1">
       <c r="A8" s="16"/>
       <c r="B8" s="17"/>
       <c r="C8" s="17"/>
-      <c r="D8" s="17"/>
-      <c r="E8" s="18"/>
     </row>
     <row r="9" spans="1:8" ht="42" customHeight="1">
       <c r="A9" s="16"/>
       <c r="B9" s="17"/>
       <c r="C9" s="17"/>
-      <c r="D9" s="17"/>
-      <c r="E9" s="18"/>
     </row>
     <row r="10" spans="1:8" ht="42" customHeight="1">
       <c r="A10" s="16"/>
       <c r="B10" s="17"/>
       <c r="C10" s="17"/>
-      <c r="D10" s="17"/>
-      <c r="E10" s="18"/>
     </row>
     <row r="11" spans="1:8" ht="42" customHeight="1">
       <c r="A11" s="16"/>
       <c r="B11" s="17"/>
       <c r="C11" s="17"/>
-      <c r="D11" s="17"/>
-      <c r="E11" s="18"/>
     </row>
     <row r="12" spans="1:8" ht="42" customHeight="1">
       <c r="A12" s="16"/>
       <c r="B12" s="17"/>
       <c r="C12" s="17"/>
-      <c r="D12" s="17"/>
-      <c r="E12" s="18"/>
     </row>
     <row r="13" spans="1:8" ht="42" customHeight="1">
       <c r="A13" s="16"/>
@@ -1813,65 +1898,41 @@
       <c r="E21" s="18"/>
     </row>
     <row r="22" spans="1:5" ht="42" customHeight="1">
-      <c r="A22" s="16"/>
-      <c r="B22" s="17"/>
-      <c r="C22" s="17"/>
+      <c r="A22" s="19"/>
+      <c r="B22" s="20"/>
+      <c r="C22" s="20"/>
       <c r="D22" s="17"/>
       <c r="E22" s="18"/>
     </row>
     <row r="23" spans="1:5" ht="42" customHeight="1">
-      <c r="A23" s="16"/>
-      <c r="B23" s="17"/>
-      <c r="C23" s="17"/>
       <c r="D23" s="17"/>
       <c r="E23" s="18"/>
     </row>
     <row r="24" spans="1:5" ht="42" customHeight="1">
-      <c r="A24" s="16"/>
-      <c r="B24" s="17"/>
-      <c r="C24" s="17"/>
       <c r="D24" s="17"/>
       <c r="E24" s="18"/>
     </row>
     <row r="25" spans="1:5" ht="42" customHeight="1">
-      <c r="A25" s="16"/>
-      <c r="B25" s="17"/>
-      <c r="C25" s="17"/>
       <c r="D25" s="17"/>
       <c r="E25" s="18"/>
     </row>
     <row r="26" spans="1:5" ht="42" customHeight="1">
-      <c r="A26" s="16"/>
-      <c r="B26" s="17"/>
-      <c r="C26" s="17"/>
       <c r="D26" s="17"/>
       <c r="E26" s="18"/>
     </row>
     <row r="27" spans="1:5" ht="42" customHeight="1">
-      <c r="A27" s="16"/>
-      <c r="B27" s="17"/>
-      <c r="C27" s="17"/>
       <c r="D27" s="17"/>
       <c r="E27" s="18"/>
     </row>
     <row r="28" spans="1:5" ht="42" customHeight="1">
-      <c r="A28" s="16"/>
-      <c r="B28" s="17"/>
-      <c r="C28" s="17"/>
       <c r="D28" s="17"/>
       <c r="E28" s="18"/>
     </row>
     <row r="29" spans="1:5" ht="42" customHeight="1">
-      <c r="A29" s="16"/>
-      <c r="B29" s="17"/>
-      <c r="C29" s="17"/>
       <c r="D29" s="17"/>
       <c r="E29" s="18"/>
     </row>
     <row r="30" spans="1:5" ht="42" customHeight="1">
-      <c r="A30" s="19"/>
-      <c r="B30" s="20"/>
-      <c r="C30" s="20"/>
       <c r="D30" s="20"/>
       <c r="E30" s="21"/>
     </row>
@@ -1879,7 +1940,7 @@
   <mergeCells count="1">
     <mergeCell ref="G1:H1"/>
   </mergeCells>
-  <conditionalFormatting sqref="A2:A30">
+  <conditionalFormatting sqref="A5:A22">
     <cfRule type="duplicateValues" dxfId="3" priority="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="H4">
@@ -1888,11 +1949,11 @@
     <cfRule type="containsText" dxfId="0" priority="4" operator="containsText" text="Automatische verdeling"/>
   </conditionalFormatting>
   <dataValidations count="2">
-    <dataValidation type="whole" sqref="A2:A30" xr:uid="{00000000-0002-0000-0100-000000000000}">
+    <dataValidation type="whole" sqref="A5:A22" xr:uid="{00000000-0002-0000-0100-000000000000}">
       <formula1>1</formula1>
       <formula2>100</formula2>
     </dataValidation>
-    <dataValidation type="whole" sqref="D2:D30" xr:uid="{00000000-0002-0000-0100-000001000000}">
+    <dataValidation type="whole" sqref="D13:D30" xr:uid="{00000000-0002-0000-0100-000001000000}">
       <formula1>1</formula1>
       <formula2>250</formula2>
     </dataValidation>
@@ -1915,19 +1976,19 @@
   <sheetData>
     <row r="1" spans="1:6">
       <c r="A1" s="24" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="B1" s="25" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="C1" s="25" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="D1" s="25" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="E1" s="25" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="F1" s="26" t="s">
         <v>3</v>
@@ -1935,14 +1996,14 @@
     </row>
     <row r="2" spans="1:6" ht="31.95" customHeight="1">
       <c r="A2" s="27" t="s">
-        <v>80</v>
+        <v>52</v>
       </c>
       <c r="B2" s="28"/>
       <c r="C2" s="28"/>
       <c r="D2" s="28"/>
       <c r="E2" s="28"/>
       <c r="F2" s="29" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
     </row>
     <row r="3" spans="1:6" ht="31.95" customHeight="1">
@@ -1952,7 +2013,7 @@
       <c r="D3" s="28"/>
       <c r="E3" s="28"/>
       <c r="F3" s="29" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
     </row>
     <row r="4" spans="1:6" ht="31.95" customHeight="1">
@@ -1962,7 +2023,7 @@
       <c r="D4" s="28"/>
       <c r="E4" s="28"/>
       <c r="F4" s="29" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
     </row>
     <row r="5" spans="1:6" ht="31.95" customHeight="1">
@@ -1972,7 +2033,7 @@
       <c r="D5" s="28"/>
       <c r="E5" s="28"/>
       <c r="F5" s="29" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
     </row>
     <row r="6" spans="1:6" ht="31.95" customHeight="1">
@@ -1982,7 +2043,7 @@
       <c r="D6" s="28"/>
       <c r="E6" s="28"/>
       <c r="F6" s="29" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
     </row>
     <row r="7" spans="1:6" ht="31.95" customHeight="1">
@@ -2095,19 +2156,19 @@
   <sheetData>
     <row r="1" spans="1:6">
       <c r="A1" s="33" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B1" s="34" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="C1" s="34" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="D1" s="34" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="E1" s="34" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="F1" s="35" t="s">
         <v>3</v>
@@ -2120,7 +2181,7 @@
       <c r="D2" s="37"/>
       <c r="E2" s="37"/>
       <c r="F2" s="38" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
     </row>
     <row r="3" spans="1:6" ht="31.95" customHeight="1">
@@ -2130,7 +2191,7 @@
       <c r="D3" s="37"/>
       <c r="E3" s="37"/>
       <c r="F3" s="38" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
     </row>
     <row r="4" spans="1:6" ht="31.95" customHeight="1">
@@ -2140,7 +2201,7 @@
       <c r="D4" s="37"/>
       <c r="E4" s="37"/>
       <c r="F4" s="38" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
     </row>
     <row r="5" spans="1:6" ht="31.95" customHeight="1">
@@ -2150,7 +2211,7 @@
       <c r="D5" s="37"/>
       <c r="E5" s="37"/>
       <c r="F5" s="38" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
     </row>
     <row r="6" spans="1:6" ht="31.95" customHeight="1">
@@ -2160,7 +2221,7 @@
       <c r="D6" s="37"/>
       <c r="E6" s="37"/>
       <c r="F6" s="38" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
     </row>
     <row r="7" spans="1:6" ht="31.95" customHeight="1">
@@ -2170,7 +2231,7 @@
       <c r="D7" s="37"/>
       <c r="E7" s="37"/>
       <c r="F7" s="38" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
     </row>
     <row r="8" spans="1:6" ht="31.95" customHeight="1">
@@ -2265,19 +2326,19 @@
   <sheetData>
     <row r="1" spans="1:6">
       <c r="A1" s="42" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B1" s="43" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="C1" s="43" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="D1" s="43" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="E1" s="43" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="F1" s="44" t="s">
         <v>3</v>
@@ -2290,7 +2351,7 @@
       <c r="D2" s="46"/>
       <c r="E2" s="46"/>
       <c r="F2" s="47" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
     </row>
     <row r="3" spans="1:6" ht="37.950000000000003" customHeight="1">
@@ -2300,7 +2361,7 @@
       <c r="D3" s="46"/>
       <c r="E3" s="46"/>
       <c r="F3" s="47" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
     </row>
     <row r="4" spans="1:6" ht="37.950000000000003" customHeight="1">
@@ -2310,7 +2371,7 @@
       <c r="D4" s="46"/>
       <c r="E4" s="46"/>
       <c r="F4" s="47" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
     </row>
     <row r="5" spans="1:6" ht="37.950000000000003" customHeight="1">
@@ -2320,7 +2381,7 @@
       <c r="D5" s="46"/>
       <c r="E5" s="46"/>
       <c r="F5" s="47" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
     </row>
     <row r="6" spans="1:6" ht="37.950000000000003" customHeight="1">
@@ -2330,7 +2391,7 @@
       <c r="D6" s="46"/>
       <c r="E6" s="46"/>
       <c r="F6" s="47" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
     </row>
     <row r="7" spans="1:6" ht="37.950000000000003" customHeight="1">
@@ -2340,7 +2401,7 @@
       <c r="D7" s="46"/>
       <c r="E7" s="46"/>
       <c r="F7" s="47" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
     </row>
     <row r="8" spans="1:6" ht="37.950000000000003" customHeight="1">
@@ -2350,7 +2411,7 @@
       <c r="D8" s="46"/>
       <c r="E8" s="46"/>
       <c r="F8" s="47" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
     </row>
     <row r="9" spans="1:6" ht="37.950000000000003" customHeight="1">

--- a/patient_settings_uitgebreid.xlsx
+++ b/patient_settings_uitgebreid.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Vivian\Desktop\Master onderzoek\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5EE97CCD-B687-4908-8A5E-E2759C4D7E45}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{87A660D2-E054-4A2C-A8A9-BB75998BCB39}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Patient" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="107" uniqueCount="90">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="117" uniqueCount="99">
   <si>
     <t>PATIËNTINSTELLINGEN</t>
   </si>
@@ -87,226 +87,253 @@
     <t>ruis_spelfouten</t>
   </si>
   <si>
+    <t>Kies Geen, Laag of Gemiddeld: opzettelijke kleine type- of spelfouten in vrije tekst.</t>
+  </si>
+  <si>
+    <t>ruis_afkortingen</t>
+  </si>
+  <si>
+    <t>Kies Geen, Laag of Gemiddeld: gebruik van gangbare Nederlandse medische afkortingen.</t>
+  </si>
+  <si>
+    <t>ruis_telegramstijl</t>
+  </si>
+  <si>
+    <t>Kies Geen, Laag of Gemiddeld: beknopte zinsdelen en het weglaten van bijvoorbeeld lidwoorden.</t>
+  </si>
+  <si>
+    <t>ruis_interpunctie</t>
+  </si>
+  <si>
+    <t>Kies Geen, Laag of Gemiddeld: inconsistente punten, komma's en hoofdletters in vrije tekst.</t>
+  </si>
+  <si>
+    <t>ruis_herhaling</t>
+  </si>
+  <si>
+    <t>Kies Geen, Laag of Gemiddeld: beperkte herhaling van relevante voorgeschiedenis of eerder beleid.</t>
+  </si>
+  <si>
+    <t>allergie_modus</t>
+  </si>
+  <si>
+    <t>Automatisch</t>
+  </si>
+  <si>
+    <t>Automatisch, Zelf invoeren of Geen. Bij Zelf invoeren gebruik je het tabblad Allergieen.</t>
+  </si>
+  <si>
+    <t>microbiologie_modus</t>
+  </si>
+  <si>
+    <t>Automatisch, Zelf invoeren of Geen. Bij Zelf invoeren gebruik je het tabblad Microbiologie.</t>
+  </si>
+  <si>
+    <t>laboratorium_modus</t>
+  </si>
+  <si>
+    <t>Automatisch, Zelf invoeren of Geen. Bij Zelf invoeren gebruik je het tabblad Laboratorium.</t>
+  </si>
+  <si>
+    <t>volgorde</t>
+  </si>
+  <si>
+    <t>episode</t>
+  </si>
+  <si>
+    <t>patient_specifieke_omschrijving</t>
+  </si>
+  <si>
+    <t>CONTROLE DEELCONTACTEN</t>
+  </si>
+  <si>
+    <t>Essentiële hypertensie</t>
+  </si>
+  <si>
+    <t>Totaal per episode</t>
+  </si>
+  <si>
+    <t>Diabetes mellitus type 2</t>
+  </si>
+  <si>
+    <t>Totaal tabblad Patient</t>
+  </si>
+  <si>
+    <t>Controle</t>
+  </si>
+  <si>
+    <t>allergeen</t>
+  </si>
+  <si>
+    <t>type_allergie</t>
+  </si>
+  <si>
+    <t>reactie</t>
+  </si>
+  <si>
+    <t>ernst</t>
+  </si>
+  <si>
+    <t>status</t>
+  </si>
+  <si>
+    <t>Kiwi</t>
+  </si>
+  <si>
+    <t>Alleen gebruikt als allergie_modus op Zelf invoeren staat.</t>
+  </si>
+  <si>
+    <t>Vul minimaal het allergeen in, bijvoorbeeld penicilline.</t>
+  </si>
+  <si>
+    <t>Andere velden mogen leeg blijven; dan kiest het model een passende waarde.</t>
+  </si>
+  <si>
+    <t>Bij Automatisch worden deze regels genegeerd en beslist het model zelf.</t>
+  </si>
+  <si>
+    <t>Bij Geen blijft het allergieoverzicht leeg.</t>
+  </si>
+  <si>
+    <t>materiaal</t>
+  </si>
+  <si>
+    <t>onderzoek</t>
+  </si>
+  <si>
+    <t>gewenste_uitslag</t>
+  </si>
+  <si>
+    <t>verwekker</t>
+  </si>
+  <si>
+    <t>Alleen gebruikt als microbiologie_modus op Zelf invoeren staat.</t>
+  </si>
+  <si>
+    <t>Vul bijvoorbeeld: urineweginfectie | urine | urinekweek.</t>
+  </si>
+  <si>
+    <t>Gewenste uitslag kan bijvoorbeeld positief of negatief zijn, of leeg blijven.</t>
+  </si>
+  <si>
+    <t>De verwekker mag leeg blijven; dan kiest het model een passende uitkomst.</t>
+  </si>
+  <si>
+    <t>Bij Geen blijft de microbiologielijst leeg.</t>
+  </si>
+  <si>
+    <t>aanvraagreden</t>
+  </si>
+  <si>
+    <t>bepaling</t>
+  </si>
+  <si>
+    <t>gewenste_waarde</t>
+  </si>
+  <si>
+    <t>eenheid</t>
+  </si>
+  <si>
+    <t>Alleen gebruikt als laboratorium_modus op Zelf invoeren staat.</t>
+  </si>
+  <si>
+    <t>Vul minimaal de bepaling in, bijvoorbeeld HbA1c, creatinine of TSH.</t>
+  </si>
+  <si>
+    <t>Episode, aanvraagreden, gewenste waarde en eenheid mogen leeg blijven; dan vult het model dit automatisch in.</t>
+  </si>
+  <si>
+    <t>Vul voor meerdere bepalingen meerdere regels in; de code laat passende waarden onder één prikmoment groeperen.</t>
+  </si>
+  <si>
+    <t>Bij Automatisch maakt het model realistische laboratoriumaanvragen met meerdere samenhangende bepalingen.</t>
+  </si>
+  <si>
+    <t>Ook normale nevenbepalingen kunnen worden opgenomen; een volledig bloedbeeld wordt niet bij elke hypertensiecontrole afgedwongen.</t>
+  </si>
+  <si>
+    <t>Bij Geen blijft de lijst met laboratoriumuitslagen leeg.</t>
+  </si>
+  <si>
+    <t>rookstatus</t>
+  </si>
+  <si>
+    <t>Laat op Automatisch staan of vul zelf in, bijvoorbeeld: voormalig roker, 20 pack-years, gestopt in 2012.</t>
+  </si>
+  <si>
+    <t>alcoholgebruik</t>
+  </si>
+  <si>
+    <t>Laat op Automatisch staan of vul zelf een realistisch gebruik in, bijvoorbeeld: 4 eenheden per week.</t>
+  </si>
+  <si>
+    <t>familieanamnese</t>
+  </si>
+  <si>
+    <t>Laat op Automatisch staan of specificeer klinisch relevante familieanamnese; bijvoorbeeld hart- en vaatziekten bij een eerstegraads familielid.</t>
+  </si>
+  <si>
+    <t>woonsituatie</t>
+  </si>
+  <si>
+    <t>Laat op Automatisch staan of specificeer bijvoorbeeld alleenwonend, samenwonend, mantelzorg of thuiszorg.</t>
+  </si>
+  <si>
+    <t>beroep_functionele_context</t>
+  </si>
+  <si>
+    <t>Laat op Automatisch staan of beschrijf beroep/dagbesteding en relevante zelfstandigheid, mobiliteit of hulpmiddelen.</t>
+  </si>
+  <si>
+    <t>1 pakje per dag</t>
+  </si>
+  <si>
+    <t>Hypercholesterolemie</t>
+  </si>
+  <si>
+    <t>Artrose van beide knieën</t>
+  </si>
+  <si>
+    <t>Constitutioneel eczeem</t>
+  </si>
+  <si>
+    <t>Mictieklachten bij de man</t>
+  </si>
+  <si>
+    <t>Cataract beiderzijds</t>
+  </si>
+  <si>
+    <t>Urineweginfectie</t>
+  </si>
+  <si>
+    <t>Leeftijdsgebonden gehoorverlies</t>
+  </si>
+  <si>
+    <t>Chronische nierschade stadium G3a</t>
+  </si>
+  <si>
+    <t>Actinische keratose</t>
+  </si>
+  <si>
+    <t>Ischemisch cerebrovasculair accident</t>
+  </si>
+  <si>
+    <t>Atriumfibrilleren</t>
+  </si>
+  <si>
+    <t>Pneumonie</t>
+  </si>
+  <si>
+    <t>Valincident zonder fractuur</t>
+  </si>
+  <si>
+    <t>Obstipatie</t>
+  </si>
+  <si>
+    <t>P012</t>
+  </si>
+  <si>
     <t>Laag</t>
-  </si>
-  <si>
-    <t>Kies Geen, Laag of Gemiddeld: opzettelijke kleine type- of spelfouten in vrije tekst.</t>
-  </si>
-  <si>
-    <t>ruis_afkortingen</t>
-  </si>
-  <si>
-    <t>Kies Geen, Laag of Gemiddeld: gebruik van gangbare Nederlandse medische afkortingen.</t>
-  </si>
-  <si>
-    <t>ruis_telegramstijl</t>
-  </si>
-  <si>
-    <t>Kies Geen, Laag of Gemiddeld: beknopte zinsdelen en het weglaten van bijvoorbeeld lidwoorden.</t>
-  </si>
-  <si>
-    <t>ruis_interpunctie</t>
-  </si>
-  <si>
-    <t>Geen</t>
-  </si>
-  <si>
-    <t>Kies Geen, Laag of Gemiddeld: inconsistente punten, komma's en hoofdletters in vrije tekst.</t>
-  </si>
-  <si>
-    <t>ruis_herhaling</t>
-  </si>
-  <si>
-    <t>Kies Geen, Laag of Gemiddeld: beperkte herhaling van relevante voorgeschiedenis of eerder beleid.</t>
-  </si>
-  <si>
-    <t>allergie_modus</t>
-  </si>
-  <si>
-    <t>Automatisch</t>
-  </si>
-  <si>
-    <t>Automatisch, Zelf invoeren of Geen. Bij Zelf invoeren gebruik je het tabblad Allergieen.</t>
-  </si>
-  <si>
-    <t>microbiologie_modus</t>
-  </si>
-  <si>
-    <t>Automatisch, Zelf invoeren of Geen. Bij Zelf invoeren gebruik je het tabblad Microbiologie.</t>
-  </si>
-  <si>
-    <t>laboratorium_modus</t>
-  </si>
-  <si>
-    <t>Automatisch, Zelf invoeren of Geen. Bij Zelf invoeren gebruik je het tabblad Laboratorium.</t>
-  </si>
-  <si>
-    <t>volgorde</t>
-  </si>
-  <si>
-    <t>episode</t>
-  </si>
-  <si>
-    <t>patient_specifieke_omschrijving</t>
-  </si>
-  <si>
-    <t>CONTROLE DEELCONTACTEN</t>
-  </si>
-  <si>
-    <t>Essentiële hypertensie</t>
-  </si>
-  <si>
-    <t>Langdurig bekend, meestal redelijk gereguleerd met enkele hogere metingen</t>
-  </si>
-  <si>
-    <t>Totaal per episode</t>
-  </si>
-  <si>
-    <t>Diabetes mellitus type 2</t>
-  </si>
-  <si>
-    <t>Jaarcontroles, wisselende HbA1c-waarden en aandacht voor leefstijl en medicatie</t>
-  </si>
-  <si>
-    <t>Totaal tabblad Patient</t>
-  </si>
-  <si>
-    <t>Controle</t>
-  </si>
-  <si>
-    <t>Valincident met huidwond</t>
-  </si>
-  <si>
-    <t>Cerebraal infarct</t>
-  </si>
-  <si>
-    <t>allergeen</t>
-  </si>
-  <si>
-    <t>type_allergie</t>
-  </si>
-  <si>
-    <t>reactie</t>
-  </si>
-  <si>
-    <t>ernst</t>
-  </si>
-  <si>
-    <t>status</t>
-  </si>
-  <si>
-    <t>Kiwi</t>
-  </si>
-  <si>
-    <t>Alleen gebruikt als allergie_modus op Zelf invoeren staat.</t>
-  </si>
-  <si>
-    <t>Vul minimaal het allergeen in, bijvoorbeeld penicilline.</t>
-  </si>
-  <si>
-    <t>Andere velden mogen leeg blijven; dan kiest het model een passende waarde.</t>
-  </si>
-  <si>
-    <t>Bij Automatisch worden deze regels genegeerd en beslist het model zelf.</t>
-  </si>
-  <si>
-    <t>Bij Geen blijft het allergieoverzicht leeg.</t>
-  </si>
-  <si>
-    <t>materiaal</t>
-  </si>
-  <si>
-    <t>onderzoek</t>
-  </si>
-  <si>
-    <t>gewenste_uitslag</t>
-  </si>
-  <si>
-    <t>verwekker</t>
-  </si>
-  <si>
-    <t>Alleen gebruikt als microbiologie_modus op Zelf invoeren staat.</t>
-  </si>
-  <si>
-    <t>Vul bijvoorbeeld: urineweginfectie | urine | urinekweek.</t>
-  </si>
-  <si>
-    <t>Gewenste uitslag kan bijvoorbeeld positief of negatief zijn, of leeg blijven.</t>
-  </si>
-  <si>
-    <t>De verwekker mag leeg blijven; dan kiest het model een passende uitkomst.</t>
-  </si>
-  <si>
-    <t>Bij Geen blijft de microbiologielijst leeg.</t>
-  </si>
-  <si>
-    <t>aanvraagreden</t>
-  </si>
-  <si>
-    <t>bepaling</t>
-  </si>
-  <si>
-    <t>gewenste_waarde</t>
-  </si>
-  <si>
-    <t>eenheid</t>
-  </si>
-  <si>
-    <t>Alleen gebruikt als laboratorium_modus op Zelf invoeren staat.</t>
-  </si>
-  <si>
-    <t>Vul minimaal de bepaling in, bijvoorbeeld HbA1c, creatinine of TSH.</t>
-  </si>
-  <si>
-    <t>Episode, aanvraagreden, gewenste waarde en eenheid mogen leeg blijven; dan vult het model dit automatisch in.</t>
-  </si>
-  <si>
-    <t>Vul voor meerdere bepalingen meerdere regels in; de code laat passende waarden onder één prikmoment groeperen.</t>
-  </si>
-  <si>
-    <t>Bij Automatisch maakt het model realistische laboratoriumaanvragen met meerdere samenhangende bepalingen.</t>
-  </si>
-  <si>
-    <t>Ook normale nevenbepalingen kunnen worden opgenomen; een volledig bloedbeeld wordt niet bij elke hypertensiecontrole afgedwongen.</t>
-  </si>
-  <si>
-    <t>Bij Geen blijft de lijst met laboratoriumuitslagen leeg.</t>
-  </si>
-  <si>
-    <t>rookstatus</t>
-  </si>
-  <si>
-    <t>Laat op Automatisch staan of vul zelf in, bijvoorbeeld: voormalig roker, 20 pack-years, gestopt in 2012.</t>
-  </si>
-  <si>
-    <t>alcoholgebruik</t>
-  </si>
-  <si>
-    <t>Laat op Automatisch staan of vul zelf een realistisch gebruik in, bijvoorbeeld: 4 eenheden per week.</t>
-  </si>
-  <si>
-    <t>familieanamnese</t>
-  </si>
-  <si>
-    <t>Laat op Automatisch staan of specificeer klinisch relevante familieanamnese; bijvoorbeeld hart- en vaatziekten bij een eerstegraads familielid.</t>
-  </si>
-  <si>
-    <t>woonsituatie</t>
-  </si>
-  <si>
-    <t>Laat op Automatisch staan of specificeer bijvoorbeeld alleenwonend, samenwonend, mantelzorg of thuiszorg.</t>
-  </si>
-  <si>
-    <t>beroep_functionele_context</t>
-  </si>
-  <si>
-    <t>Laat op Automatisch staan of beschrijf beroep/dagbesteding en relevante zelfstandigheid, mobiliteit of hulpmiddelen.</t>
-  </si>
-  <si>
-    <t>P010</t>
-  </si>
-  <si>
-    <t>1 pakje per dag</t>
   </si>
 </sst>
 </file>
@@ -444,7 +471,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="47">
+  <borders count="46">
     <border>
       <left/>
       <right/>
@@ -630,19 +657,6 @@
       </left>
       <right/>
       <top/>
-      <bottom style="thin">
-        <color rgb="FFD9E2F3"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color rgb="FFD9E2F3"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFD9E2F3"/>
-      </top>
       <bottom style="thin">
         <color rgb="FFD9E2F3"/>
       </bottom>
@@ -1023,7 +1037,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="57">
+  <cellXfs count="56">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1073,24 +1087,24 @@
     <xf numFmtId="0" fontId="0" fillId="5" borderId="16" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="17" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="18" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="17" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="18" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="19" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="20" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="21" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="22" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="22" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="20" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="21" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="21" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="8" borderId="22" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="8" borderId="23" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
@@ -1098,26 +1112,26 @@
     <xf numFmtId="0" fontId="2" fillId="8" borderId="24" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="8" borderId="25" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="25" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="26" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="9" borderId="27" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="28" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="29" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="9" borderId="30" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="10" borderId="31" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="26" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="27" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="9" borderId="28" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="29" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="30" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="9" borderId="31" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="10" borderId="32" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
@@ -1125,26 +1139,26 @@
     <xf numFmtId="0" fontId="2" fillId="10" borderId="33" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="10" borderId="34" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="34" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="35" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="11" borderId="36" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="37" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="38" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="11" borderId="39" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="40" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="35" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="36" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="11" borderId="37" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="38" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="39" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="11" borderId="40" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="41" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
@@ -1152,25 +1166,22 @@
     <xf numFmtId="0" fontId="2" fillId="2" borderId="42" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="43" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="22" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="21" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="4" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="43" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="44" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="45" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="46" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="45" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -1185,11 +1196,11 @@
     <xf numFmtId="0" fontId="4" fillId="14" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="21" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="22" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -1480,7 +1491,7 @@
         <v>4</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>88</v>
+        <v>97</v>
       </c>
       <c r="C4" s="6" t="s">
         <v>5</v>
@@ -1513,7 +1524,7 @@
         <v>11</v>
       </c>
       <c r="B7" s="8">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="C7" s="9" t="s">
         <v>12</v>
@@ -1524,7 +1535,7 @@
         <v>13</v>
       </c>
       <c r="B8" s="8">
-        <v>10</v>
+        <v>140</v>
       </c>
       <c r="C8" s="9" t="s">
         <v>14</v>
@@ -1535,142 +1546,142 @@
         <v>15</v>
       </c>
       <c r="B9" s="8" t="s">
+        <v>98</v>
+      </c>
+      <c r="C9" s="9" t="s">
         <v>16</v>
-      </c>
-      <c r="C9" s="9" t="s">
-        <v>17</v>
       </c>
     </row>
     <row r="10" spans="1:3" ht="36" customHeight="1">
       <c r="A10" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="B10" s="8" t="s">
+        <v>98</v>
+      </c>
+      <c r="C10" s="9" t="s">
         <v>18</v>
-      </c>
-      <c r="B10" s="8" t="s">
-        <v>16</v>
-      </c>
-      <c r="C10" s="9" t="s">
-        <v>19</v>
       </c>
     </row>
     <row r="11" spans="1:3" ht="36" customHeight="1">
       <c r="A11" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="B11" s="8" t="s">
+        <v>98</v>
+      </c>
+      <c r="C11" s="9" t="s">
         <v>20</v>
-      </c>
-      <c r="B11" s="8" t="s">
-        <v>16</v>
-      </c>
-      <c r="C11" s="9" t="s">
-        <v>21</v>
       </c>
     </row>
     <row r="12" spans="1:3" ht="36" customHeight="1">
       <c r="A12" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="B12" s="8" t="s">
+        <v>98</v>
+      </c>
+      <c r="C12" s="9" t="s">
         <v>22</v>
-      </c>
-      <c r="B12" s="8" t="s">
-        <v>23</v>
-      </c>
-      <c r="C12" s="9" t="s">
-        <v>24</v>
       </c>
     </row>
     <row r="13" spans="1:3" ht="36" customHeight="1">
       <c r="A13" s="7" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="B13" s="8" t="s">
-        <v>16</v>
+        <v>98</v>
       </c>
       <c r="C13" s="9" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
     </row>
     <row r="14" spans="1:3" ht="36" customHeight="1">
       <c r="A14" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="B14" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="C14" s="9" t="s">
         <v>27</v>
-      </c>
-      <c r="B14" s="8" t="s">
-        <v>28</v>
-      </c>
-      <c r="C14" s="9" t="s">
-        <v>29</v>
       </c>
     </row>
     <row r="15" spans="1:3" ht="36" customHeight="1">
       <c r="A15" s="7" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="B15" s="8" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="C15" s="9" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
     </row>
     <row r="16" spans="1:3" ht="36" customHeight="1">
       <c r="A16" s="10" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="B16" s="11" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="C16" s="12" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
     </row>
     <row r="17" spans="1:3" ht="48" customHeight="1">
-      <c r="A17" s="52" t="s">
+      <c r="A17" s="51" t="s">
+        <v>72</v>
+      </c>
+      <c r="B17" s="52" t="s">
+        <v>82</v>
+      </c>
+      <c r="C17" s="53" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" ht="48" customHeight="1">
+      <c r="A18" s="51" t="s">
+        <v>74</v>
+      </c>
+      <c r="B18" s="52" t="s">
+        <v>26</v>
+      </c>
+      <c r="C18" s="53" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" ht="48" customHeight="1">
+      <c r="A19" s="51" t="s">
+        <v>76</v>
+      </c>
+      <c r="B19" s="52" t="s">
+        <v>26</v>
+      </c>
+      <c r="C19" s="53" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" ht="48" customHeight="1">
+      <c r="A20" s="51" t="s">
         <v>78</v>
       </c>
-      <c r="B17" s="53" t="s">
-        <v>89</v>
-      </c>
-      <c r="C17" s="54" t="s">
+      <c r="B20" s="52" t="s">
+        <v>26</v>
+      </c>
+      <c r="C20" s="53" t="s">
         <v>79</v>
       </c>
     </row>
-    <row r="18" spans="1:3" ht="48" customHeight="1">
-      <c r="A18" s="52" t="s">
+    <row r="21" spans="1:3" ht="48" customHeight="1">
+      <c r="A21" s="51" t="s">
         <v>80</v>
       </c>
-      <c r="B18" s="53" t="s">
-        <v>28</v>
-      </c>
-      <c r="C18" s="54" t="s">
+      <c r="B21" s="52" t="s">
+        <v>26</v>
+      </c>
+      <c r="C21" s="53" t="s">
         <v>81</v>
-      </c>
-    </row>
-    <row r="19" spans="1:3" ht="48" customHeight="1">
-      <c r="A19" s="52" t="s">
-        <v>82</v>
-      </c>
-      <c r="B19" s="53" t="s">
-        <v>28</v>
-      </c>
-      <c r="C19" s="54" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="20" spans="1:3" ht="48" customHeight="1">
-      <c r="A20" s="52" t="s">
-        <v>84</v>
-      </c>
-      <c r="B20" s="53" t="s">
-        <v>28</v>
-      </c>
-      <c r="C20" s="54" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="21" spans="1:3" ht="48" customHeight="1">
-      <c r="A21" s="52" t="s">
-        <v>86</v>
-      </c>
-      <c r="B21" s="53" t="s">
-        <v>28</v>
-      </c>
-      <c r="C21" s="54" t="s">
-        <v>87</v>
       </c>
     </row>
   </sheetData>
@@ -1720,13 +1731,13 @@
   <sheetData>
     <row r="1" spans="1:8">
       <c r="A1" s="13" t="s">
+        <v>32</v>
+      </c>
+      <c r="B1" s="14" t="s">
+        <v>33</v>
+      </c>
+      <c r="C1" s="14" t="s">
         <v>34</v>
-      </c>
-      <c r="B1" s="14" t="s">
-        <v>35</v>
-      </c>
-      <c r="C1" s="14" t="s">
-        <v>36</v>
       </c>
       <c r="D1" s="14" t="s">
         <v>13</v>
@@ -1734,213 +1745,265 @@
       <c r="E1" s="15" t="s">
         <v>3</v>
       </c>
-      <c r="G1" s="56" t="s">
+      <c r="G1" s="54" t="s">
+        <v>35</v>
+      </c>
+      <c r="H1" s="54"/>
+    </row>
+    <row r="2" spans="1:8" ht="42" customHeight="1">
+      <c r="A2" s="50">
+        <v>1</v>
+      </c>
+      <c r="B2" t="s">
+        <v>36</v>
+      </c>
+      <c r="C2" s="50"/>
+      <c r="G2" s="21" t="s">
         <v>37</v>
       </c>
-      <c r="H1" s="56"/>
-    </row>
-    <row r="2" spans="1:8" ht="42" customHeight="1">
-      <c r="A2" s="51">
-        <v>1</v>
-      </c>
-      <c r="B2" s="51" t="s">
-        <v>38</v>
-      </c>
-      <c r="C2" s="51" t="s">
-        <v>39</v>
-      </c>
-      <c r="G2" s="22" t="s">
-        <v>40</v>
-      </c>
-      <c r="H2" s="23">
+      <c r="H2" s="22">
         <f>SUM(D2:D30)</f>
         <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:8" ht="42" customHeight="1">
-      <c r="A3" s="51">
+      <c r="A3" s="50">
         <v>2</v>
       </c>
-      <c r="B3" s="51" t="s">
-        <v>41</v>
-      </c>
-      <c r="C3" s="51" t="s">
-        <v>42</v>
-      </c>
-      <c r="G3" s="22" t="s">
-        <v>43</v>
-      </c>
-      <c r="H3" s="23">
+      <c r="B3" t="s">
+        <v>83</v>
+      </c>
+      <c r="C3" s="50"/>
+      <c r="G3" s="21" t="s">
+        <v>39</v>
+      </c>
+      <c r="H3" s="22">
         <f>Patient!B8</f>
-        <v>10</v>
+        <v>140</v>
       </c>
     </row>
     <row r="4" spans="1:8" ht="42" customHeight="1">
-      <c r="A4" s="51">
-        <v>11</v>
-      </c>
-      <c r="B4" s="51" t="s">
-        <v>45</v>
-      </c>
-      <c r="G4" s="22" t="s">
-        <v>44</v>
-      </c>
-      <c r="H4" s="23" t="str">
+      <c r="A4" s="50">
+        <v>3</v>
+      </c>
+      <c r="B4" t="s">
+        <v>84</v>
+      </c>
+      <c r="G4" s="21" t="s">
+        <v>40</v>
+      </c>
+      <c r="H4" s="22" t="str">
         <f>IF(COUNT(D2:D30)=0,"Automatische verdeling",IF(H2=H3,"Klopt","Verschil"))</f>
         <v>Automatische verdeling</v>
       </c>
     </row>
     <row r="5" spans="1:8" ht="42" customHeight="1">
-      <c r="A5" s="16">
+      <c r="A5" s="50">
+        <v>4</v>
+      </c>
+      <c r="B5" t="s">
+        <v>38</v>
+      </c>
+      <c r="C5" s="16"/>
+    </row>
+    <row r="6" spans="1:8" ht="42" customHeight="1">
+      <c r="A6" s="50">
+        <v>5</v>
+      </c>
+      <c r="B6" s="50"/>
+      <c r="C6" s="16"/>
+    </row>
+    <row r="7" spans="1:8" ht="42" customHeight="1">
+      <c r="A7" s="50">
+        <v>6</v>
+      </c>
+      <c r="B7" s="50" t="s">
+        <v>85</v>
+      </c>
+      <c r="C7" s="16"/>
+    </row>
+    <row r="8" spans="1:8" ht="42" customHeight="1">
+      <c r="A8" s="50">
+        <v>7</v>
+      </c>
+      <c r="B8" t="s">
+        <v>86</v>
+      </c>
+      <c r="C8" s="16"/>
+    </row>
+    <row r="9" spans="1:8" ht="42" customHeight="1">
+      <c r="A9" s="50">
+        <v>8</v>
+      </c>
+      <c r="B9" t="s">
+        <v>87</v>
+      </c>
+      <c r="C9" s="16"/>
+    </row>
+    <row r="10" spans="1:8" ht="42" customHeight="1">
+      <c r="A10" s="50">
+        <v>9</v>
+      </c>
+      <c r="B10" t="s">
+        <v>88</v>
+      </c>
+      <c r="C10" s="16"/>
+    </row>
+    <row r="11" spans="1:8" ht="42" customHeight="1">
+      <c r="A11" s="50">
+        <v>10</v>
+      </c>
+      <c r="B11" t="s">
+        <v>89</v>
+      </c>
+      <c r="C11" s="16"/>
+    </row>
+    <row r="12" spans="1:8" ht="42" customHeight="1">
+      <c r="A12" s="50">
+        <v>11</v>
+      </c>
+      <c r="B12" t="s">
+        <v>90</v>
+      </c>
+      <c r="C12" s="16"/>
+    </row>
+    <row r="13" spans="1:8" ht="42" customHeight="1">
+      <c r="A13" s="50">
         <v>12</v>
       </c>
-      <c r="B5" s="17" t="s">
-        <v>46</v>
-      </c>
-      <c r="C5" s="17"/>
-    </row>
-    <row r="6" spans="1:8" ht="42" customHeight="1">
-      <c r="A6" s="16"/>
-      <c r="B6" s="17"/>
-      <c r="C6" s="17"/>
-    </row>
-    <row r="7" spans="1:8" ht="42" customHeight="1">
-      <c r="A7" s="16"/>
-      <c r="B7" s="17"/>
-      <c r="C7" s="17"/>
-    </row>
-    <row r="8" spans="1:8" ht="42" customHeight="1">
-      <c r="A8" s="16"/>
-      <c r="B8" s="17"/>
-      <c r="C8" s="17"/>
-    </row>
-    <row r="9" spans="1:8" ht="42" customHeight="1">
-      <c r="A9" s="16"/>
-      <c r="B9" s="17"/>
-      <c r="C9" s="17"/>
-    </row>
-    <row r="10" spans="1:8" ht="42" customHeight="1">
-      <c r="A10" s="16"/>
-      <c r="B10" s="17"/>
-      <c r="C10" s="17"/>
-    </row>
-    <row r="11" spans="1:8" ht="42" customHeight="1">
-      <c r="A11" s="16"/>
-      <c r="B11" s="17"/>
-      <c r="C11" s="17"/>
-    </row>
-    <row r="12" spans="1:8" ht="42" customHeight="1">
-      <c r="A12" s="16"/>
-      <c r="B12" s="17"/>
-      <c r="C12" s="17"/>
-    </row>
-    <row r="13" spans="1:8" ht="42" customHeight="1">
-      <c r="A13" s="16"/>
-      <c r="B13" s="17"/>
-      <c r="C13" s="17"/>
-      <c r="D13" s="17"/>
-      <c r="E13" s="18"/>
+      <c r="B13" s="50"/>
+      <c r="C13" s="16"/>
+      <c r="D13" s="16"/>
+      <c r="E13" s="17"/>
     </row>
     <row r="14" spans="1:8" ht="42" customHeight="1">
-      <c r="A14" s="16"/>
-      <c r="B14" s="17"/>
-      <c r="C14" s="17"/>
-      <c r="D14" s="17"/>
-      <c r="E14" s="18"/>
+      <c r="A14" s="50">
+        <v>13</v>
+      </c>
+      <c r="B14" s="50" t="s">
+        <v>91</v>
+      </c>
+      <c r="C14" s="16"/>
+      <c r="D14" s="16"/>
+      <c r="E14" s="17"/>
     </row>
     <row r="15" spans="1:8" ht="42" customHeight="1">
-      <c r="A15" s="16"/>
-      <c r="B15" s="17"/>
-      <c r="C15" s="17"/>
-      <c r="D15" s="17"/>
-      <c r="E15" s="18"/>
+      <c r="A15" s="50">
+        <v>14</v>
+      </c>
+      <c r="B15" s="50"/>
+      <c r="C15" s="16"/>
+      <c r="D15" s="16"/>
+      <c r="E15" s="17"/>
     </row>
     <row r="16" spans="1:8" ht="42" customHeight="1">
-      <c r="A16" s="16"/>
-      <c r="B16" s="17"/>
-      <c r="C16" s="17"/>
-      <c r="D16" s="17"/>
-      <c r="E16" s="18"/>
+      <c r="A16" s="50">
+        <v>15</v>
+      </c>
+      <c r="B16" s="50" t="s">
+        <v>92</v>
+      </c>
+      <c r="C16" s="16"/>
+      <c r="D16" s="16"/>
+      <c r="E16" s="17"/>
     </row>
     <row r="17" spans="1:5" ht="42" customHeight="1">
-      <c r="A17" s="16"/>
-      <c r="B17" s="17"/>
-      <c r="C17" s="17"/>
-      <c r="D17" s="17"/>
-      <c r="E17" s="18"/>
+      <c r="A17" s="50">
+        <v>16</v>
+      </c>
+      <c r="B17" s="50"/>
+      <c r="C17" s="16"/>
+      <c r="D17" s="16"/>
+      <c r="E17" s="17"/>
     </row>
     <row r="18" spans="1:5" ht="42" customHeight="1">
-      <c r="A18" s="16"/>
-      <c r="B18" s="17"/>
-      <c r="C18" s="17"/>
-      <c r="D18" s="17"/>
-      <c r="E18" s="18"/>
+      <c r="A18" s="50">
+        <v>17</v>
+      </c>
+      <c r="B18" s="50" t="s">
+        <v>93</v>
+      </c>
+      <c r="C18" s="16"/>
+      <c r="D18" s="16"/>
+      <c r="E18" s="17"/>
     </row>
     <row r="19" spans="1:5" ht="42" customHeight="1">
-      <c r="A19" s="16"/>
-      <c r="B19" s="17"/>
-      <c r="C19" s="17"/>
-      <c r="D19" s="17"/>
-      <c r="E19" s="18"/>
+      <c r="A19" s="50">
+        <v>18</v>
+      </c>
+      <c r="B19" t="s">
+        <v>94</v>
+      </c>
+      <c r="C19" s="16"/>
+      <c r="D19" s="16"/>
+      <c r="E19" s="17"/>
     </row>
     <row r="20" spans="1:5" ht="42" customHeight="1">
-      <c r="A20" s="16"/>
-      <c r="B20" s="17"/>
-      <c r="C20" s="17"/>
-      <c r="D20" s="17"/>
-      <c r="E20" s="18"/>
+      <c r="A20" s="50">
+        <v>19</v>
+      </c>
+      <c r="B20" t="s">
+        <v>95</v>
+      </c>
+      <c r="C20" s="16"/>
+      <c r="D20" s="16"/>
+      <c r="E20" s="17"/>
     </row>
     <row r="21" spans="1:5" ht="42" customHeight="1">
-      <c r="A21" s="16"/>
-      <c r="B21" s="17"/>
-      <c r="C21" s="17"/>
-      <c r="D21" s="17"/>
-      <c r="E21" s="18"/>
+      <c r="A21" s="50">
+        <v>20</v>
+      </c>
+      <c r="B21" t="s">
+        <v>96</v>
+      </c>
+      <c r="C21" s="16"/>
+      <c r="D21" s="16"/>
+      <c r="E21" s="17"/>
     </row>
     <row r="22" spans="1:5" ht="42" customHeight="1">
-      <c r="A22" s="19"/>
-      <c r="B22" s="20"/>
-      <c r="C22" s="20"/>
-      <c r="D22" s="17"/>
-      <c r="E22" s="18"/>
+      <c r="A22" s="18"/>
+      <c r="B22" s="19"/>
+      <c r="C22" s="19"/>
+      <c r="D22" s="16"/>
+      <c r="E22" s="17"/>
     </row>
     <row r="23" spans="1:5" ht="42" customHeight="1">
-      <c r="D23" s="17"/>
-      <c r="E23" s="18"/>
+      <c r="D23" s="16"/>
+      <c r="E23" s="17"/>
     </row>
     <row r="24" spans="1:5" ht="42" customHeight="1">
-      <c r="D24" s="17"/>
-      <c r="E24" s="18"/>
+      <c r="D24" s="16"/>
+      <c r="E24" s="17"/>
     </row>
     <row r="25" spans="1:5" ht="42" customHeight="1">
-      <c r="D25" s="17"/>
-      <c r="E25" s="18"/>
+      <c r="D25" s="16"/>
+      <c r="E25" s="17"/>
     </row>
     <row r="26" spans="1:5" ht="42" customHeight="1">
-      <c r="D26" s="17"/>
-      <c r="E26" s="18"/>
+      <c r="D26" s="16"/>
+      <c r="E26" s="17"/>
     </row>
     <row r="27" spans="1:5" ht="42" customHeight="1">
-      <c r="D27" s="17"/>
-      <c r="E27" s="18"/>
+      <c r="D27" s="16"/>
+      <c r="E27" s="17"/>
     </row>
     <row r="28" spans="1:5" ht="42" customHeight="1">
-      <c r="D28" s="17"/>
-      <c r="E28" s="18"/>
+      <c r="D28" s="16"/>
+      <c r="E28" s="17"/>
     </row>
     <row r="29" spans="1:5" ht="42" customHeight="1">
-      <c r="D29" s="17"/>
-      <c r="E29" s="18"/>
+      <c r="D29" s="16"/>
+      <c r="E29" s="17"/>
     </row>
     <row r="30" spans="1:5" ht="42" customHeight="1">
-      <c r="D30" s="20"/>
-      <c r="E30" s="21"/>
+      <c r="D30" s="19"/>
+      <c r="E30" s="20"/>
     </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="G1:H1"/>
   </mergeCells>
-  <conditionalFormatting sqref="A5:A22">
+  <conditionalFormatting sqref="A22">
     <cfRule type="duplicateValues" dxfId="3" priority="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="H4">
@@ -1949,7 +2012,7 @@
     <cfRule type="containsText" dxfId="0" priority="4" operator="containsText" text="Automatische verdeling"/>
   </conditionalFormatting>
   <dataValidations count="2">
-    <dataValidation type="whole" sqref="A5:A22" xr:uid="{00000000-0002-0000-0100-000000000000}">
+    <dataValidation type="whole" sqref="A22" xr:uid="{00000000-0002-0000-0100-000000000000}">
       <formula1>1</formula1>
       <formula2>100</formula2>
     </dataValidation>
@@ -1975,156 +2038,156 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6">
-      <c r="A1" s="24" t="s">
+      <c r="A1" s="23" t="s">
+        <v>41</v>
+      </c>
+      <c r="B1" s="24" t="s">
+        <v>42</v>
+      </c>
+      <c r="C1" s="24" t="s">
+        <v>43</v>
+      </c>
+      <c r="D1" s="24" t="s">
+        <v>44</v>
+      </c>
+      <c r="E1" s="24" t="s">
+        <v>45</v>
+      </c>
+      <c r="F1" s="25" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" ht="31.95" customHeight="1">
+      <c r="A2" s="26" t="s">
+        <v>46</v>
+      </c>
+      <c r="B2" s="27"/>
+      <c r="C2" s="27"/>
+      <c r="D2" s="27"/>
+      <c r="E2" s="27"/>
+      <c r="F2" s="28" t="s">
         <v>47</v>
       </c>
-      <c r="B1" s="25" t="s">
+    </row>
+    <row r="3" spans="1:6" ht="31.95" customHeight="1">
+      <c r="A3" s="26"/>
+      <c r="B3" s="27"/>
+      <c r="C3" s="27"/>
+      <c r="D3" s="27"/>
+      <c r="E3" s="27"/>
+      <c r="F3" s="28" t="s">
         <v>48</v>
       </c>
-      <c r="C1" s="25" t="s">
+    </row>
+    <row r="4" spans="1:6" ht="31.95" customHeight="1">
+      <c r="A4" s="26"/>
+      <c r="B4" s="27"/>
+      <c r="C4" s="27"/>
+      <c r="D4" s="27"/>
+      <c r="E4" s="27"/>
+      <c r="F4" s="28" t="s">
         <v>49</v>
       </c>
-      <c r="D1" s="25" t="s">
+    </row>
+    <row r="5" spans="1:6" ht="31.95" customHeight="1">
+      <c r="A5" s="26"/>
+      <c r="B5" s="27"/>
+      <c r="C5" s="27"/>
+      <c r="D5" s="27"/>
+      <c r="E5" s="27"/>
+      <c r="F5" s="28" t="s">
         <v>50</v>
       </c>
-      <c r="E1" s="25" t="s">
+    </row>
+    <row r="6" spans="1:6" ht="31.95" customHeight="1">
+      <c r="A6" s="26"/>
+      <c r="B6" s="27"/>
+      <c r="C6" s="27"/>
+      <c r="D6" s="27"/>
+      <c r="E6" s="27"/>
+      <c r="F6" s="28" t="s">
         <v>51</v>
       </c>
-      <c r="F1" s="26" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6" ht="31.95" customHeight="1">
-      <c r="A2" s="27" t="s">
-        <v>52</v>
-      </c>
-      <c r="B2" s="28"/>
-      <c r="C2" s="28"/>
-      <c r="D2" s="28"/>
-      <c r="E2" s="28"/>
-      <c r="F2" s="29" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6" ht="31.95" customHeight="1">
-      <c r="A3" s="27"/>
-      <c r="B3" s="28"/>
-      <c r="C3" s="28"/>
-      <c r="D3" s="28"/>
-      <c r="E3" s="28"/>
-      <c r="F3" s="29" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6" ht="31.95" customHeight="1">
-      <c r="A4" s="27"/>
-      <c r="B4" s="28"/>
-      <c r="C4" s="28"/>
-      <c r="D4" s="28"/>
-      <c r="E4" s="28"/>
-      <c r="F4" s="29" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" ht="31.95" customHeight="1">
-      <c r="A5" s="27"/>
-      <c r="B5" s="28"/>
-      <c r="C5" s="28"/>
-      <c r="D5" s="28"/>
-      <c r="E5" s="28"/>
-      <c r="F5" s="29" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6" ht="31.95" customHeight="1">
-      <c r="A6" s="27"/>
-      <c r="B6" s="28"/>
-      <c r="C6" s="28"/>
-      <c r="D6" s="28"/>
-      <c r="E6" s="28"/>
-      <c r="F6" s="29" t="s">
-        <v>57</v>
-      </c>
     </row>
     <row r="7" spans="1:6" ht="31.95" customHeight="1">
-      <c r="A7" s="27"/>
-      <c r="B7" s="28"/>
-      <c r="C7" s="28"/>
-      <c r="D7" s="28"/>
-      <c r="E7" s="28"/>
-      <c r="F7" s="29"/>
+      <c r="A7" s="26"/>
+      <c r="B7" s="27"/>
+      <c r="C7" s="27"/>
+      <c r="D7" s="27"/>
+      <c r="E7" s="27"/>
+      <c r="F7" s="28"/>
     </row>
     <row r="8" spans="1:6" ht="31.95" customHeight="1">
-      <c r="A8" s="27"/>
-      <c r="B8" s="28"/>
-      <c r="C8" s="28"/>
-      <c r="D8" s="28"/>
-      <c r="E8" s="28"/>
-      <c r="F8" s="29"/>
+      <c r="A8" s="26"/>
+      <c r="B8" s="27"/>
+      <c r="C8" s="27"/>
+      <c r="D8" s="27"/>
+      <c r="E8" s="27"/>
+      <c r="F8" s="28"/>
     </row>
     <row r="9" spans="1:6" ht="31.95" customHeight="1">
-      <c r="A9" s="27"/>
-      <c r="B9" s="28"/>
-      <c r="C9" s="28"/>
-      <c r="D9" s="28"/>
-      <c r="E9" s="28"/>
-      <c r="F9" s="29"/>
+      <c r="A9" s="26"/>
+      <c r="B9" s="27"/>
+      <c r="C9" s="27"/>
+      <c r="D9" s="27"/>
+      <c r="E9" s="27"/>
+      <c r="F9" s="28"/>
     </row>
     <row r="10" spans="1:6" ht="31.95" customHeight="1">
-      <c r="A10" s="27"/>
-      <c r="B10" s="28"/>
-      <c r="C10" s="28"/>
-      <c r="D10" s="28"/>
-      <c r="E10" s="28"/>
-      <c r="F10" s="29"/>
+      <c r="A10" s="26"/>
+      <c r="B10" s="27"/>
+      <c r="C10" s="27"/>
+      <c r="D10" s="27"/>
+      <c r="E10" s="27"/>
+      <c r="F10" s="28"/>
     </row>
     <row r="11" spans="1:6" ht="31.95" customHeight="1">
-      <c r="A11" s="27"/>
-      <c r="B11" s="28"/>
-      <c r="C11" s="28"/>
-      <c r="D11" s="28"/>
-      <c r="E11" s="28"/>
-      <c r="F11" s="29"/>
+      <c r="A11" s="26"/>
+      <c r="B11" s="27"/>
+      <c r="C11" s="27"/>
+      <c r="D11" s="27"/>
+      <c r="E11" s="27"/>
+      <c r="F11" s="28"/>
     </row>
     <row r="12" spans="1:6" ht="31.95" customHeight="1">
-      <c r="A12" s="27"/>
-      <c r="B12" s="28"/>
-      <c r="C12" s="28"/>
-      <c r="D12" s="28"/>
-      <c r="E12" s="28"/>
-      <c r="F12" s="29"/>
+      <c r="A12" s="26"/>
+      <c r="B12" s="27"/>
+      <c r="C12" s="27"/>
+      <c r="D12" s="27"/>
+      <c r="E12" s="27"/>
+      <c r="F12" s="28"/>
     </row>
     <row r="13" spans="1:6" ht="31.95" customHeight="1">
-      <c r="A13" s="27"/>
-      <c r="B13" s="28"/>
-      <c r="C13" s="28"/>
-      <c r="D13" s="28"/>
-      <c r="E13" s="28"/>
-      <c r="F13" s="29"/>
+      <c r="A13" s="26"/>
+      <c r="B13" s="27"/>
+      <c r="C13" s="27"/>
+      <c r="D13" s="27"/>
+      <c r="E13" s="27"/>
+      <c r="F13" s="28"/>
     </row>
     <row r="14" spans="1:6" ht="31.95" customHeight="1">
-      <c r="A14" s="27"/>
-      <c r="B14" s="28"/>
-      <c r="C14" s="28"/>
-      <c r="D14" s="28"/>
-      <c r="E14" s="28"/>
-      <c r="F14" s="29"/>
+      <c r="A14" s="26"/>
+      <c r="B14" s="27"/>
+      <c r="C14" s="27"/>
+      <c r="D14" s="27"/>
+      <c r="E14" s="27"/>
+      <c r="F14" s="28"/>
     </row>
     <row r="15" spans="1:6" ht="31.95" customHeight="1">
-      <c r="A15" s="27"/>
-      <c r="B15" s="28"/>
-      <c r="C15" s="28"/>
-      <c r="D15" s="28"/>
-      <c r="E15" s="28"/>
-      <c r="F15" s="29"/>
+      <c r="A15" s="26"/>
+      <c r="B15" s="27"/>
+      <c r="C15" s="27"/>
+      <c r="D15" s="27"/>
+      <c r="E15" s="27"/>
+      <c r="F15" s="28"/>
     </row>
     <row r="16" spans="1:6" ht="31.95" customHeight="1">
-      <c r="A16" s="30"/>
-      <c r="B16" s="31"/>
-      <c r="C16" s="31"/>
-      <c r="D16" s="31"/>
-      <c r="E16" s="31"/>
-      <c r="F16" s="32"/>
+      <c r="A16" s="29"/>
+      <c r="B16" s="30"/>
+      <c r="C16" s="30"/>
+      <c r="D16" s="30"/>
+      <c r="E16" s="30"/>
+      <c r="F16" s="31"/>
     </row>
   </sheetData>
   <dataValidations count="3">
@@ -2155,156 +2218,156 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6">
-      <c r="A1" s="33" t="s">
-        <v>35</v>
-      </c>
-      <c r="B1" s="34" t="s">
+      <c r="A1" s="32" t="s">
+        <v>33</v>
+      </c>
+      <c r="B1" s="33" t="s">
+        <v>52</v>
+      </c>
+      <c r="C1" s="33" t="s">
+        <v>53</v>
+      </c>
+      <c r="D1" s="33" t="s">
+        <v>54</v>
+      </c>
+      <c r="E1" s="33" t="s">
+        <v>55</v>
+      </c>
+      <c r="F1" s="34" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" ht="31.95" customHeight="1">
+      <c r="A2" s="35"/>
+      <c r="B2" s="36"/>
+      <c r="C2" s="36"/>
+      <c r="D2" s="36"/>
+      <c r="E2" s="36"/>
+      <c r="F2" s="37" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" ht="31.95" customHeight="1">
+      <c r="A3" s="35"/>
+      <c r="B3" s="36"/>
+      <c r="C3" s="36"/>
+      <c r="D3" s="36"/>
+      <c r="E3" s="36"/>
+      <c r="F3" s="37" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" ht="31.95" customHeight="1">
+      <c r="A4" s="35"/>
+      <c r="B4" s="36"/>
+      <c r="C4" s="36"/>
+      <c r="D4" s="36"/>
+      <c r="E4" s="36"/>
+      <c r="F4" s="37" t="s">
         <v>58</v>
       </c>
-      <c r="C1" s="34" t="s">
+    </row>
+    <row r="5" spans="1:6" ht="31.95" customHeight="1">
+      <c r="A5" s="35"/>
+      <c r="B5" s="36"/>
+      <c r="C5" s="36"/>
+      <c r="D5" s="36"/>
+      <c r="E5" s="36"/>
+      <c r="F5" s="37" t="s">
         <v>59</v>
       </c>
-      <c r="D1" s="34" t="s">
+    </row>
+    <row r="6" spans="1:6" ht="31.95" customHeight="1">
+      <c r="A6" s="35"/>
+      <c r="B6" s="36"/>
+      <c r="C6" s="36"/>
+      <c r="D6" s="36"/>
+      <c r="E6" s="36"/>
+      <c r="F6" s="37" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" ht="31.95" customHeight="1">
+      <c r="A7" s="35"/>
+      <c r="B7" s="36"/>
+      <c r="C7" s="36"/>
+      <c r="D7" s="36"/>
+      <c r="E7" s="36"/>
+      <c r="F7" s="37" t="s">
         <v>60</v>
       </c>
-      <c r="E1" s="34" t="s">
-        <v>61</v>
-      </c>
-      <c r="F1" s="35" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6" ht="31.95" customHeight="1">
-      <c r="A2" s="36"/>
-      <c r="B2" s="37"/>
-      <c r="C2" s="37"/>
-      <c r="D2" s="37"/>
-      <c r="E2" s="37"/>
-      <c r="F2" s="38" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6" ht="31.95" customHeight="1">
-      <c r="A3" s="36"/>
-      <c r="B3" s="37"/>
-      <c r="C3" s="37"/>
-      <c r="D3" s="37"/>
-      <c r="E3" s="37"/>
-      <c r="F3" s="38" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6" ht="31.95" customHeight="1">
-      <c r="A4" s="36"/>
-      <c r="B4" s="37"/>
-      <c r="C4" s="37"/>
-      <c r="D4" s="37"/>
-      <c r="E4" s="37"/>
-      <c r="F4" s="38" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" ht="31.95" customHeight="1">
-      <c r="A5" s="36"/>
-      <c r="B5" s="37"/>
-      <c r="C5" s="37"/>
-      <c r="D5" s="37"/>
-      <c r="E5" s="37"/>
-      <c r="F5" s="38" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6" ht="31.95" customHeight="1">
-      <c r="A6" s="36"/>
-      <c r="B6" s="37"/>
-      <c r="C6" s="37"/>
-      <c r="D6" s="37"/>
-      <c r="E6" s="37"/>
-      <c r="F6" s="38" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6" ht="31.95" customHeight="1">
-      <c r="A7" s="36"/>
-      <c r="B7" s="37"/>
-      <c r="C7" s="37"/>
-      <c r="D7" s="37"/>
-      <c r="E7" s="37"/>
-      <c r="F7" s="38" t="s">
-        <v>66</v>
-      </c>
     </row>
     <row r="8" spans="1:6" ht="31.95" customHeight="1">
-      <c r="A8" s="36"/>
-      <c r="B8" s="37"/>
-      <c r="C8" s="37"/>
-      <c r="D8" s="37"/>
-      <c r="E8" s="37"/>
-      <c r="F8" s="38"/>
+      <c r="A8" s="35"/>
+      <c r="B8" s="36"/>
+      <c r="C8" s="36"/>
+      <c r="D8" s="36"/>
+      <c r="E8" s="36"/>
+      <c r="F8" s="37"/>
     </row>
     <row r="9" spans="1:6" ht="31.95" customHeight="1">
-      <c r="A9" s="36"/>
-      <c r="B9" s="37"/>
-      <c r="C9" s="37"/>
-      <c r="D9" s="37"/>
-      <c r="E9" s="37"/>
-      <c r="F9" s="38"/>
+      <c r="A9" s="35"/>
+      <c r="B9" s="36"/>
+      <c r="C9" s="36"/>
+      <c r="D9" s="36"/>
+      <c r="E9" s="36"/>
+      <c r="F9" s="37"/>
     </row>
     <row r="10" spans="1:6" ht="31.95" customHeight="1">
-      <c r="A10" s="36"/>
-      <c r="B10" s="37"/>
-      <c r="C10" s="37"/>
-      <c r="D10" s="37"/>
-      <c r="E10" s="37"/>
-      <c r="F10" s="38"/>
+      <c r="A10" s="35"/>
+      <c r="B10" s="36"/>
+      <c r="C10" s="36"/>
+      <c r="D10" s="36"/>
+      <c r="E10" s="36"/>
+      <c r="F10" s="37"/>
     </row>
     <row r="11" spans="1:6" ht="31.95" customHeight="1">
-      <c r="A11" s="36"/>
-      <c r="B11" s="37"/>
-      <c r="C11" s="37"/>
-      <c r="D11" s="37"/>
-      <c r="E11" s="37"/>
-      <c r="F11" s="38"/>
+      <c r="A11" s="35"/>
+      <c r="B11" s="36"/>
+      <c r="C11" s="36"/>
+      <c r="D11" s="36"/>
+      <c r="E11" s="36"/>
+      <c r="F11" s="37"/>
     </row>
     <row r="12" spans="1:6" ht="31.95" customHeight="1">
-      <c r="A12" s="36"/>
-      <c r="B12" s="37"/>
-      <c r="C12" s="37"/>
-      <c r="D12" s="37"/>
-      <c r="E12" s="37"/>
-      <c r="F12" s="38"/>
+      <c r="A12" s="35"/>
+      <c r="B12" s="36"/>
+      <c r="C12" s="36"/>
+      <c r="D12" s="36"/>
+      <c r="E12" s="36"/>
+      <c r="F12" s="37"/>
     </row>
     <row r="13" spans="1:6" ht="31.95" customHeight="1">
-      <c r="A13" s="36"/>
-      <c r="B13" s="37"/>
-      <c r="C13" s="37"/>
-      <c r="D13" s="37"/>
-      <c r="E13" s="37"/>
-      <c r="F13" s="38"/>
+      <c r="A13" s="35"/>
+      <c r="B13" s="36"/>
+      <c r="C13" s="36"/>
+      <c r="D13" s="36"/>
+      <c r="E13" s="36"/>
+      <c r="F13" s="37"/>
     </row>
     <row r="14" spans="1:6" ht="31.95" customHeight="1">
-      <c r="A14" s="36"/>
-      <c r="B14" s="37"/>
-      <c r="C14" s="37"/>
-      <c r="D14" s="37"/>
-      <c r="E14" s="37"/>
-      <c r="F14" s="38"/>
+      <c r="A14" s="35"/>
+      <c r="B14" s="36"/>
+      <c r="C14" s="36"/>
+      <c r="D14" s="36"/>
+      <c r="E14" s="36"/>
+      <c r="F14" s="37"/>
     </row>
     <row r="15" spans="1:6" ht="31.95" customHeight="1">
-      <c r="A15" s="36"/>
-      <c r="B15" s="37"/>
-      <c r="C15" s="37"/>
-      <c r="D15" s="37"/>
-      <c r="E15" s="37"/>
-      <c r="F15" s="38"/>
+      <c r="A15" s="35"/>
+      <c r="B15" s="36"/>
+      <c r="C15" s="36"/>
+      <c r="D15" s="36"/>
+      <c r="E15" s="36"/>
+      <c r="F15" s="37"/>
     </row>
     <row r="16" spans="1:6" ht="31.95" customHeight="1">
-      <c r="A16" s="39"/>
-      <c r="B16" s="40"/>
-      <c r="C16" s="40"/>
-      <c r="D16" s="40"/>
-      <c r="E16" s="40"/>
-      <c r="F16" s="41"/>
+      <c r="A16" s="38"/>
+      <c r="B16" s="39"/>
+      <c r="C16" s="39"/>
+      <c r="D16" s="39"/>
+      <c r="E16" s="39"/>
+      <c r="F16" s="40"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -2325,158 +2388,158 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6">
-      <c r="A1" s="42" t="s">
-        <v>35</v>
-      </c>
-      <c r="B1" s="43" t="s">
+      <c r="A1" s="41" t="s">
+        <v>33</v>
+      </c>
+      <c r="B1" s="42" t="s">
+        <v>61</v>
+      </c>
+      <c r="C1" s="42" t="s">
+        <v>62</v>
+      </c>
+      <c r="D1" s="42" t="s">
+        <v>63</v>
+      </c>
+      <c r="E1" s="42" t="s">
+        <v>64</v>
+      </c>
+      <c r="F1" s="43" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" ht="37.950000000000003" customHeight="1">
+      <c r="A2" s="44"/>
+      <c r="B2" s="45"/>
+      <c r="C2" s="45"/>
+      <c r="D2" s="45"/>
+      <c r="E2" s="45"/>
+      <c r="F2" s="46" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" ht="37.950000000000003" customHeight="1">
+      <c r="A3" s="44"/>
+      <c r="B3" s="45"/>
+      <c r="C3" s="45"/>
+      <c r="D3" s="45"/>
+      <c r="E3" s="45"/>
+      <c r="F3" s="46" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" ht="37.950000000000003" customHeight="1">
+      <c r="A4" s="44"/>
+      <c r="B4" s="45"/>
+      <c r="C4" s="45"/>
+      <c r="D4" s="45"/>
+      <c r="E4" s="45"/>
+      <c r="F4" s="46" t="s">
         <v>67</v>
       </c>
-      <c r="C1" s="43" t="s">
+    </row>
+    <row r="5" spans="1:6" ht="37.950000000000003" customHeight="1">
+      <c r="A5" s="44"/>
+      <c r="B5" s="45"/>
+      <c r="C5" s="45"/>
+      <c r="D5" s="45"/>
+      <c r="E5" s="45"/>
+      <c r="F5" s="46" t="s">
         <v>68</v>
       </c>
-      <c r="D1" s="43" t="s">
+    </row>
+    <row r="6" spans="1:6" ht="37.950000000000003" customHeight="1">
+      <c r="A6" s="44"/>
+      <c r="B6" s="45"/>
+      <c r="C6" s="45"/>
+      <c r="D6" s="45"/>
+      <c r="E6" s="45"/>
+      <c r="F6" s="46" t="s">
         <v>69</v>
       </c>
-      <c r="E1" s="43" t="s">
+    </row>
+    <row r="7" spans="1:6" ht="37.950000000000003" customHeight="1">
+      <c r="A7" s="44"/>
+      <c r="B7" s="45"/>
+      <c r="C7" s="45"/>
+      <c r="D7" s="45"/>
+      <c r="E7" s="45"/>
+      <c r="F7" s="46" t="s">
         <v>70</v>
       </c>
-      <c r="F1" s="44" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6" ht="37.950000000000003" customHeight="1">
-      <c r="A2" s="45"/>
-      <c r="B2" s="46"/>
-      <c r="C2" s="46"/>
-      <c r="D2" s="46"/>
-      <c r="E2" s="46"/>
-      <c r="F2" s="47" t="s">
+    </row>
+    <row r="8" spans="1:6" ht="37.950000000000003" customHeight="1">
+      <c r="A8" s="44"/>
+      <c r="B8" s="45"/>
+      <c r="C8" s="45"/>
+      <c r="D8" s="45"/>
+      <c r="E8" s="45"/>
+      <c r="F8" s="46" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="3" spans="1:6" ht="37.950000000000003" customHeight="1">
-      <c r="A3" s="45"/>
-      <c r="B3" s="46"/>
-      <c r="C3" s="46"/>
-      <c r="D3" s="46"/>
-      <c r="E3" s="46"/>
-      <c r="F3" s="47" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6" ht="37.950000000000003" customHeight="1">
-      <c r="A4" s="45"/>
-      <c r="B4" s="46"/>
-      <c r="C4" s="46"/>
-      <c r="D4" s="46"/>
-      <c r="E4" s="46"/>
-      <c r="F4" s="47" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" ht="37.950000000000003" customHeight="1">
-      <c r="A5" s="45"/>
-      <c r="B5" s="46"/>
-      <c r="C5" s="46"/>
-      <c r="D5" s="46"/>
-      <c r="E5" s="46"/>
-      <c r="F5" s="47" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6" ht="37.950000000000003" customHeight="1">
-      <c r="A6" s="45"/>
-      <c r="B6" s="46"/>
-      <c r="C6" s="46"/>
-      <c r="D6" s="46"/>
-      <c r="E6" s="46"/>
-      <c r="F6" s="47" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6" ht="37.950000000000003" customHeight="1">
-      <c r="A7" s="45"/>
-      <c r="B7" s="46"/>
-      <c r="C7" s="46"/>
-      <c r="D7" s="46"/>
-      <c r="E7" s="46"/>
-      <c r="F7" s="47" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6" ht="37.950000000000003" customHeight="1">
-      <c r="A8" s="45"/>
-      <c r="B8" s="46"/>
-      <c r="C8" s="46"/>
-      <c r="D8" s="46"/>
-      <c r="E8" s="46"/>
-      <c r="F8" s="47" t="s">
-        <v>77</v>
-      </c>
-    </row>
     <row r="9" spans="1:6" ht="37.950000000000003" customHeight="1">
-      <c r="A9" s="45"/>
-      <c r="B9" s="46"/>
-      <c r="C9" s="46"/>
-      <c r="D9" s="46"/>
-      <c r="E9" s="46"/>
-      <c r="F9" s="47"/>
+      <c r="A9" s="44"/>
+      <c r="B9" s="45"/>
+      <c r="C9" s="45"/>
+      <c r="D9" s="45"/>
+      <c r="E9" s="45"/>
+      <c r="F9" s="46"/>
     </row>
     <row r="10" spans="1:6" ht="37.950000000000003" customHeight="1">
-      <c r="A10" s="45"/>
-      <c r="B10" s="46"/>
-      <c r="C10" s="46"/>
-      <c r="D10" s="46"/>
-      <c r="E10" s="46"/>
-      <c r="F10" s="47"/>
+      <c r="A10" s="44"/>
+      <c r="B10" s="45"/>
+      <c r="C10" s="45"/>
+      <c r="D10" s="45"/>
+      <c r="E10" s="45"/>
+      <c r="F10" s="46"/>
     </row>
     <row r="11" spans="1:6" ht="37.950000000000003" customHeight="1">
-      <c r="A11" s="45"/>
-      <c r="B11" s="46"/>
-      <c r="C11" s="46"/>
-      <c r="D11" s="46"/>
-      <c r="E11" s="46"/>
-      <c r="F11" s="47"/>
+      <c r="A11" s="44"/>
+      <c r="B11" s="45"/>
+      <c r="C11" s="45"/>
+      <c r="D11" s="45"/>
+      <c r="E11" s="45"/>
+      <c r="F11" s="46"/>
     </row>
     <row r="12" spans="1:6" ht="37.950000000000003" customHeight="1">
-      <c r="A12" s="45"/>
-      <c r="B12" s="46"/>
-      <c r="C12" s="46"/>
-      <c r="D12" s="46"/>
-      <c r="E12" s="46"/>
-      <c r="F12" s="47"/>
+      <c r="A12" s="44"/>
+      <c r="B12" s="45"/>
+      <c r="C12" s="45"/>
+      <c r="D12" s="45"/>
+      <c r="E12" s="45"/>
+      <c r="F12" s="46"/>
     </row>
     <row r="13" spans="1:6" ht="37.950000000000003" customHeight="1">
-      <c r="A13" s="45"/>
-      <c r="B13" s="46"/>
-      <c r="C13" s="46"/>
-      <c r="D13" s="46"/>
-      <c r="E13" s="46"/>
-      <c r="F13" s="47"/>
+      <c r="A13" s="44"/>
+      <c r="B13" s="45"/>
+      <c r="C13" s="45"/>
+      <c r="D13" s="45"/>
+      <c r="E13" s="45"/>
+      <c r="F13" s="46"/>
     </row>
     <row r="14" spans="1:6" ht="37.950000000000003" customHeight="1">
-      <c r="A14" s="45"/>
-      <c r="B14" s="46"/>
-      <c r="C14" s="46"/>
-      <c r="D14" s="46"/>
-      <c r="E14" s="46"/>
-      <c r="F14" s="47"/>
+      <c r="A14" s="44"/>
+      <c r="B14" s="45"/>
+      <c r="C14" s="45"/>
+      <c r="D14" s="45"/>
+      <c r="E14" s="45"/>
+      <c r="F14" s="46"/>
     </row>
     <row r="15" spans="1:6" ht="37.950000000000003" customHeight="1">
-      <c r="A15" s="45"/>
-      <c r="B15" s="46"/>
-      <c r="C15" s="46"/>
-      <c r="D15" s="46"/>
-      <c r="E15" s="46"/>
-      <c r="F15" s="47"/>
+      <c r="A15" s="44"/>
+      <c r="B15" s="45"/>
+      <c r="C15" s="45"/>
+      <c r="D15" s="45"/>
+      <c r="E15" s="45"/>
+      <c r="F15" s="46"/>
     </row>
     <row r="16" spans="1:6" ht="37.950000000000003" customHeight="1">
-      <c r="A16" s="48"/>
-      <c r="B16" s="49"/>
-      <c r="C16" s="49"/>
-      <c r="D16" s="49"/>
-      <c r="E16" s="49"/>
-      <c r="F16" s="50"/>
+      <c r="A16" s="47"/>
+      <c r="B16" s="48"/>
+      <c r="C16" s="48"/>
+      <c r="D16" s="48"/>
+      <c r="E16" s="48"/>
+      <c r="F16" s="49"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
